--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="391">
   <si>
     <t>№</t>
   </si>
@@ -824,6 +824,21 @@
     <t>вынесено: раздел 3 — файлы гарнитур в сборку не взять: исходящая сеть среды закрыта</t>
   </si>
   <si>
+    <t>П-53</t>
+  </si>
+  <si>
+    <t>packages/ui/src/styles/components.css (прежние строки 413–432), packages/ui/src/design-system.test.ts:44</t>
+  </si>
+  <si>
+    <t>Четыре правила .objectrow* пережили снятие разметки из кода (портфель-галерея, 6cd6faa): проверка мёртвых правил засчитывала потребителем лежавшую в хранилище сборку демонстрации, собранную до снятия. Мёртвое правило маскировалось устаревшей выгрузкой</t>
+  </si>
+  <si>
+    <t>пересборка демонстрации при сдаче захода уронила проверку мёртвых правил</t>
+  </si>
+  <si>
+    <t>правила сняты; собранная демонстрация исключена из потребителей — её код и так читается из исходников. Откат: прежние стили и прежняя сборка при новом правиле дают 4 мёртвых класса, при прежнем — 0</t>
+  </si>
+  <si>
     <t>Вопрос</t>
   </si>
   <si>
@@ -977,7 +992,7 @@
     <t>—</t>
   </si>
   <si>
-    <t>52: критических 11, средних 19, лёгких 16, решений заказчика 6</t>
+    <t>53: критических 11, средних 19, лёгких 17, решений заказчика 6</t>
   </si>
   <si>
     <t>реестр, раздел 2</t>
@@ -986,13 +1001,13 @@
     <t>Закрыто правкой</t>
   </si>
   <si>
-    <t>43; ещё 1 (П-12) закрывается слиянием, 8 ждут решения</t>
+    <t>44; ещё 1 (П-12) закрывается слиянием, 8 ждут решения</t>
   </si>
   <si>
     <t>Закрытых со стражем, доказанным откатом</t>
   </si>
   <si>
-    <t>37 из 43</t>
+    <t>38 из 44</t>
   </si>
   <si>
     <t>графа «Правка и её доказательство»</t>
@@ -1082,7 +1097,7 @@
     <t>Сборка клиента</t>
   </si>
   <si>
-    <t>549,69 кБ JS (146,28 кБ gzip), 75,16 кБ CSS</t>
+    <t>549,69 кБ JS (146,28 кБ gzip), 74,6 кБ CSS</t>
   </si>
   <si>
     <t>vite build</t>
@@ -1595,7 +1610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2824,6 +2839,29 @@
       </c>
       <c r="G53" s="2" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2849,13 +2887,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2863,13 +2901,13 @@
         <v>142</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2877,13 +2915,13 @@
         <v>259</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2891,13 +2929,13 @@
         <v>147</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2905,13 +2943,13 @@
         <v>254</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2919,13 +2957,13 @@
         <v>205</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2933,13 +2971,13 @@
         <v>200</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2947,13 +2985,13 @@
         <v>264</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2961,13 +2999,13 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -2989,68 +3027,68 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -3073,184 +3111,184 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -3272,101 +3310,101 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="393">
   <si>
     <t>№</t>
   </si>
@@ -113,6 +113,9 @@
     <t>вынесено: раздел 3</t>
   </si>
   <si>
+    <t>решено 01.10.2026, в работе</t>
+  </si>
+  <si>
     <t>П-5</t>
   </si>
   <si>
@@ -846,6 +849,9 @@
   </si>
   <si>
     <t>Рекомендация</t>
+  </si>
+  <si>
+    <t>Решение 01.10.2026</t>
   </si>
   <si>
     <t>Закрытый транш и его акт переписываются задним числом правкой цены, надбавки и сторно</t>
@@ -1734,27 +1740,27 @@
         <v>31</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>13</v>
@@ -1762,22 +1768,22 @@
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>13</v>
@@ -1785,22 +1791,22 @@
     </row>
     <row r="8" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>13</v>
@@ -1808,22 +1814,22 @@
     </row>
     <row r="9" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>13</v>
@@ -1831,22 +1837,22 @@
     </row>
     <row r="10" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>13</v>
@@ -1854,22 +1860,22 @@
     </row>
     <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>13</v>
@@ -1877,22 +1883,22 @@
     </row>
     <row r="12" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>13</v>
@@ -1900,45 +1906,45 @@
     </row>
     <row r="13" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -1946,22 +1952,22 @@
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -1969,22 +1975,22 @@
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -1992,22 +1998,22 @@
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -2015,22 +2021,22 @@
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -2038,22 +2044,22 @@
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -2061,22 +2067,22 @@
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -2084,22 +2090,22 @@
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -2107,22 +2113,22 @@
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -2130,22 +2136,22 @@
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -2153,22 +2159,22 @@
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -2176,22 +2182,22 @@
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -2199,22 +2205,22 @@
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2222,22 +2228,22 @@
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>13</v>
@@ -2245,68 +2251,68 @@
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2314,22 +2320,22 @@
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2337,22 +2343,22 @@
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2360,22 +2366,22 @@
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2383,22 +2389,22 @@
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2406,22 +2412,22 @@
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2429,22 +2435,22 @@
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2452,22 +2458,22 @@
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2475,22 +2481,22 @@
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2498,22 +2504,22 @@
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2521,68 +2527,68 @@
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>31</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>13</v>
@@ -2590,22 +2596,22 @@
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>13</v>
@@ -2613,22 +2619,22 @@
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>13</v>
@@ -2636,22 +2642,22 @@
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>13</v>
@@ -2659,22 +2665,22 @@
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>13</v>
@@ -2682,22 +2688,22 @@
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>13</v>
@@ -2705,22 +2711,22 @@
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>13</v>
@@ -2728,22 +2734,22 @@
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>13</v>
@@ -2751,22 +2757,22 @@
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>13</v>
@@ -2774,91 +2780,91 @@
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>13</v>
@@ -2873,125 +2879,129 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2999,17 +3009,17 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3027,68 +3037,68 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -3111,184 +3121,184 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -3310,101 +3320,101 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -473,7 +473,10 @@
     <t>чтение кода и конфигурации</t>
   </si>
   <si>
-    <t>вынесено: раздел 3 — без отправщика писем и сообщений вход иначе не работает</t>
+    <t>решение 01.10.2026 (раздел 3): эхо — только по флагу AUTH_ECHO=1 (apps/api/src/auth/echo.ts), флаг при NODE_ENV=production — отказ запуска; поставка по умолчанию — production, порты базы, хранилища и API — на 127.0.0.1; флаг ставят сборка, рецепт стенда и .env стенда показа. verify-api поднимает второй экземпляр той же сборки без флага (молчать) и с флагом в промышленном режиме (не запуститься) и проверяет, что молчание — следствие флага, а не незнакомого адреса. Откат правила к прежнему «всё, кроме production» даёт 3 замечания, снятие отказа запуска — 1</t>
+  </si>
+  <si>
+    <t>закрыто 01.10.2026</t>
   </si>
   <si>
     <t>П-29</t>
@@ -938,10 +941,10 @@
     <t>А-12: развёртывание страницы с ветки запроса</t>
   </si>
   <si>
-    <t>правило окружения github-pages пускает только ветку по умолчанию</t>
-  </si>
-  <si>
-    <t>заказчик: Settings → Environments → github-pages → Deployment branches → claude/*</t>
+    <t>снято 01.10.2026 решением заказчика: публикация только с main, условие ветки возвращено в pages.yml</t>
+  </si>
+  <si>
+    <t>—</t>
   </si>
   <si>
     <t>П-12: узел «деньги» и правки аудита в main</t>
@@ -993,9 +996,6 @@
   </si>
   <si>
     <t>Замечаний найдено</t>
-  </si>
-  <si>
-    <t>—</t>
   </si>
   <si>
     <t>53: критических 11, средних 19, лёгких 17, решений заказчика 6</t>
@@ -2292,27 +2292,27 @@
         <v>152</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2320,22 +2320,22 @@
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2343,22 +2343,22 @@
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2389,22 +2389,22 @@
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2412,22 +2412,22 @@
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2435,22 +2435,22 @@
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>122</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2458,22 +2458,22 @@
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2504,22 +2504,22 @@
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>32</v>
@@ -2550,19 +2550,19 @@
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>31</v>
@@ -2573,22 +2573,22 @@
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>13</v>
@@ -2596,22 +2596,22 @@
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>13</v>
@@ -2619,22 +2619,22 @@
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>13</v>
@@ -2642,22 +2642,22 @@
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>13</v>
@@ -2665,22 +2665,22 @@
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>13</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>13</v>
@@ -2711,22 +2711,22 @@
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>13</v>
@@ -2734,22 +2734,22 @@
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>13</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>13</v>
@@ -2780,22 +2780,22 @@
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>32</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>32</v>
@@ -2826,22 +2826,22 @@
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>32</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>13</v>
@@ -2894,16 +2894,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2911,27 +2911,27 @@
         <v>143</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2939,69 +2939,69 @@
         <v>148</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3009,13 +3009,13 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -3037,68 +3037,68 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -3121,24 +3121,24 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>327</v>
@@ -3152,7 +3152,7 @@
         <v>329</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>330</v>
@@ -3166,7 +3166,7 @@
         <v>331</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>332</v>
@@ -3180,7 +3180,7 @@
         <v>334</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>335</v>
@@ -3278,7 +3278,7 @@
         <v>361</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>362</v>
@@ -3292,7 +3292,7 @@
         <v>364</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>365</v>
@@ -3320,7 +3320,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>367</v>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -812,7 +812,7 @@
     <t>прогон: у прораба R-99 пять записей журнала; после снятия доступа — ноль, пять записей без автора</t>
   </si>
   <si>
-    <t>вынесено: раздел 3 — правка требует изменения схемы</t>
+    <t>решение 01.10.2026 (раздел 3): поле revokedAt (миграция 20261001000000_user_revoked_at); снятие оставляет строку, удаляет сессии и ссылки и снимает назначение прорабом с записью в ленте объекта; вход по почте, коду и ссылке, выдача ссылок и выбор прораба снятого не находят; повторная выдача по той же почте или телефону возвращает ту же запись с записью «доступ возвращён». verify-api: человек правит R-99, доступ снимается, автор в ленте остаётся, сессия, письмо и новая ссылка закрыты, повторная выдача возвращает тот же опознаватель. Откат службы людей к удалению строки даёт 2 замечания, снятие отказа во входе по почте — 1</t>
   </si>
   <si>
     <t>П-52</t>
@@ -2821,7 +2821,7 @@
         <v>265</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="399">
   <si>
     <t>№</t>
   </si>
@@ -650,6 +650,9 @@
     <t>чтение кода и плана</t>
   </si>
   <si>
+    <t>решение 01.10.2026 (раздел 3): действие «Обезличить» у отказной заявки — POST /leads/:id/anonymization, поле anonymizedAt (миграция 20261001010000_lead_anonymized_at); имя, телефон, адрес и заметка заменяются условным обновлением один раз, причина отказа, стадия, ориентир и задачи остаются; запись журнала о факте без персональных данных. Журнал заявки не трогается — решено заказчиком: запись «заявка заведена» хранит имя. Лист — через подтверждение с последствиями. verify-api: только отказная, однократно, прорабу 403, карточка без имени и телефона, журнал не переписан; verify-page: гейт и шапка листа после подтверждения. Откат замены полей: verify-api — 1 замечание, verify-page — 1. Срок хранения — вместе с политикой обработки (пункт 6.2 плана)</t>
+  </si>
+  <si>
     <t>П-41</t>
   </si>
   <si>
@@ -843,6 +846,21 @@
   </si>
   <si>
     <t>правила сняты; собранная демонстрация исключена из потребителей — её код и так читается из исходников. Откат: прежние стили и прежняя сборка при новом правиле дают 4 мёртвых класса, при прежнем — 0</t>
+  </si>
+  <si>
+    <t>П-54</t>
+  </si>
+  <si>
+    <t>scripts/verify-page.mjs:3976</t>
+  </si>
+  <si>
+    <t>Проверка графика записана под календарь: «сегодня» графика — настоящая дата сервера, а обход ждал отметку текущего дня в сентябре 2026. 01.10.2026 обход покраснел без единой правки продукта — и на main, и на каждом запросе слияния</t>
+  </si>
+  <si>
+    <t>прогон 01.10.2026 на свежем стенде: «текущий день в сентябре не отмечен»</t>
+  </si>
+  <si>
+    <t>месяц сегодняшнего дня выводится из часов: в сентябре отметка ожидается только если сегодня сентябрь, затем обход шагает к месяцу сегодняшнего дня (не дальше двух лет) и ищет отметку там. Прежнее правило 01.10.2026 падает, новое проходит; за двумя годами — именованное «наполнение устарело» вместо молчаливого пропуска</t>
   </si>
   <si>
     <t>Вопрос</t>
@@ -1616,7 +1634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2565,30 +2583,30 @@
         <v>210</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>32</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>13</v>
@@ -2596,22 +2614,22 @@
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>13</v>
@@ -2619,22 +2637,22 @@
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>13</v>
@@ -2642,22 +2660,22 @@
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>13</v>
@@ -2665,22 +2683,22 @@
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>13</v>
@@ -2688,22 +2706,22 @@
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>13</v>
@@ -2711,22 +2729,22 @@
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>13</v>
@@ -2734,22 +2752,22 @@
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>13</v>
@@ -2757,22 +2775,22 @@
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>13</v>
@@ -2780,22 +2798,22 @@
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>32</v>
@@ -2803,22 +2821,22 @@
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>153</v>
@@ -2826,22 +2844,22 @@
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>32</v>
@@ -2849,25 +2867,48 @@
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2894,16 +2935,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2911,27 +2952,27 @@
         <v>143</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2939,27 +2980,27 @@
         <v>148</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2967,13 +3008,13 @@
         <v>207</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2981,27 +3022,27 @@
         <v>202</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3009,13 +3050,13 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3037,68 +3078,68 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -3121,184 +3162,184 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3320,101 +3361,101 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="400">
   <si>
     <t>№</t>
   </si>
@@ -458,7 +458,10 @@
     <t>прогон на свежем стенде</t>
   </si>
   <si>
-    <t>вынесено: раздел 3 — снимки цены и надбавки требуют изменения схемы</t>
+    <t>решение 01.10.2026 (раздел 3): правило оставлено — акт следует за сметой, — правка предупреждает. Маршрут GET /projects/:code/estimate/closed-tranches (руководителю) отдаёт закрытые транши с принятыми в них позициями; листы правки позиции и надбавки при открытии называют задетые транши, подписанные акты с датой и оплаченные транши (closed-tranches.ts). Сторно приёмки в закрытом транше предупреждением не снабжено: решение называло листы правки позиции и надбавки. Стражи: closed-tranches.test.ts — 6 тестов; verify-api — только что закрытый транш называет принятую в нём позицию, прорабу и заказчику 403; verify-page — лист надбавки по настоящему перечню, лист позиции по подставленному ответу. Откат сервера (пустой перечень): verify-api — 1, verify-page — 1; компилирующийся откат клиента (лист не спрашивает перечень): verify-page — 4</t>
+  </si>
+  <si>
+    <t>закрыто 02.10.2026</t>
   </si>
   <si>
     <t>П-28</t>
@@ -2287,50 +2290,50 @@
         <v>147</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2338,22 +2341,22 @@
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2361,22 +2364,22 @@
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2384,22 +2387,22 @@
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2407,22 +2410,22 @@
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2430,22 +2433,22 @@
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2453,22 +2456,22 @@
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>122</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2476,22 +2479,22 @@
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2499,22 +2502,22 @@
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2522,22 +2525,22 @@
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2545,22 +2548,22 @@
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>32</v>
@@ -2568,45 +2571,45 @@
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>13</v>
@@ -2614,22 +2617,22 @@
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>13</v>
@@ -2637,22 +2640,22 @@
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>13</v>
@@ -2660,22 +2663,22 @@
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>13</v>
@@ -2683,22 +2686,22 @@
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>13</v>
@@ -2706,22 +2709,22 @@
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>13</v>
@@ -2729,22 +2732,22 @@
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>13</v>
@@ -2752,22 +2755,22 @@
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>13</v>
@@ -2775,22 +2778,22 @@
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>13</v>
@@ -2798,22 +2801,22 @@
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>32</v>
@@ -2821,45 +2824,45 @@
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>32</v>
@@ -2867,22 +2870,22 @@
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>13</v>
@@ -2890,25 +2893,25 @@
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2935,16 +2938,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2952,97 +2955,97 @@
         <v>143</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3050,13 +3053,13 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3078,68 +3081,68 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -3162,184 +3165,184 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3361,101 +3364,101 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -803,7 +803,7 @@
     <t>чтение кода; проба браузером</t>
   </si>
   <si>
-    <t>вынесено: раздел 3 — отмена записанного решения</t>
+    <t>решение 01.10.2026 (раздел 3): адреса вида #projects, #R-99, #R-99/estimate без новой зависимости (apps/web/src/route.ts). Оболочка держит раздел, объект и вкладку и выводит из них адрес: переход кладёт запись в историю, «Назад», «Вперёд», перезагрузка и адрес, набранный руками, возвращают экран; объект ищется в списке своей роли, закрытый раздел и чужой объект поправляются заменой записи истории. Щелчок с Ctrl, Cmd, Shift и средней кнопкой оставлен браузеру — ссылка открывается в новой вкладке. Стражи: route.test.ts — 18 тестов разбора и сборки адреса; verify-page — вход, раздел, объект, вкладка, «Назад» дважды, «Вперёд» дважды, перезагрузка, ссылка в новой вкладке, несуществующий объект. Откат четырёх файлов клиента к прежнему состоянию (компилируется) даёт 13 замечаний</t>
   </si>
   <si>
     <t>П-51</t>
@@ -2819,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -638,7 +638,7 @@
     <t>чтение кода: файл пишется в хранилище байт в байт</t>
   </si>
   <si>
-    <t>вынесено: раздел 3 — снять EXIF без искажения нельзя без новой зависимости: ориентация кадра с телефона живёт в том же сегменте, и обрезка без поворота пикселей положит снимки набок</t>
+    <t>решение 01.10.2026 (раздел 3): зависимость sharp 0.35.5 в apps/api (готовые сборки под glibc и musl, сценариев установки не требует); apps/api/src/common/clean-image.ts поворачивает кадр по ориентации и перекодирует без метаданных снимки приёмки, чеков и планы обмера, тип файла сохраняется; нечитаемый снимок — отказ словами. Образ Docker с sharp не собирался: демона Docker в среде нет. verify-api: чек загружается снимком с моделью устройства, координатами и ориентацией 6 и скачивается без EXIF и повёрнутым 48×24 → 24×48. Откат (файл кладётся как есть, компилируется) даёт 2 замечания</t>
   </si>
   <si>
     <t>П-40</t>
@@ -2566,7 +2566,7 @@
         <v>207</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="399">
   <si>
     <t>№</t>
   </si>
@@ -833,7 +833,7 @@
     <t>чтение кода; обход песочницы фиксирует отказ узла гарнитур</t>
   </si>
   <si>
-    <t>вынесено: раздел 3 — файлы гарнитур в сборку не взять: исходящая сеть среды закрыта</t>
+    <t>решение 01.10.2026 (раздел 3): 18 файлов woff2 (Golos Text и IBM Plex Mono, 400/500/600; кириллица, латиница и расширенная латиница со знаком ₽; 220 КБ) из пакетов @fontsource 5.3.0 под OFL 1.1 — в packages/ui/src/fonts вместе с текстами лицензий; fonts.css объявляет их @font-face. Публикация копирует файлы в site/fonts и подменяет ссылки страниц своей таблицей (scripts/fonts.mjs); версии для артефактов (*.artifact.html, design/demo.html) сохраняют ссылку — так решено. Стражи: design-system.test.ts — слой стилей без внешних адресов, объявленные файлы и лицензии на месте; verify-page и verify-demo — обращение к Google Fonts есть дефект, а не сеть песочницы; verify-pages — ни один опубликованный файл к Google не обращается, файлы таблицы на месте. Откат продукта к @import Google: тесты — 4 падения, verify-demo и verify-pages — замечания; откат подмены при публикации: verify-pages — 18</t>
   </si>
   <si>
     <t>П-53</t>
@@ -980,10 +980,7 @@
     <t>П-52, вариант а</t>
   </si>
   <si>
-    <t>исходящая сеть среды закрыта для узла гарнитур — файлов woff2 не получить</t>
-  </si>
-  <si>
-    <t>заказчик — решением; сборка — в среде с сетью</t>
+    <t>снято 02.10.2026: файлы получены из реестра npm (@fontsource), сеть к нему открыта</t>
   </si>
   <si>
     <t>Опечатка «Окрывные работы» в исходной смете</t>
@@ -2865,7 +2862,7 @@
         <v>272</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3120,29 +3117,29 @@
         <v>321</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -3165,184 +3162,184 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>316</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>316</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>316</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>316</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>316</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>316</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3367,98 +3364,98 @@
         <v>311</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
   </sheetData>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="426">
   <si>
     <t>№</t>
   </si>
@@ -233,10 +233,7 @@
     <t>git merge-base --is-ancestor a4bb019 origin/main — нет</t>
   </si>
   <si>
-    <t>закрывается сдачей захода: запрос слияния в main вместе с правками аудита</t>
-  </si>
-  <si>
-    <t>в работе</t>
+    <t>закрывается сдачей захода: запрос слияния в main вместе с правками аудита; слит в main запросом #46 (900dfad, 30.09.2026), git merge-base --is-ancestor a4bb019 origin/main — да</t>
   </si>
   <si>
     <t>П-13</t>
@@ -971,10 +968,7 @@
     <t>П-12: узел «деньги» и правки аудита в main</t>
   </si>
   <si>
-    <t>слияние запроса — шаг сдачи захода</t>
-  </si>
-  <si>
-    <t>сдача захода</t>
+    <t>снято: запрос #46 слит 30.09.2026 (900dfad)</t>
   </si>
   <si>
     <t>П-52, вариант а</t>
@@ -1134,6 +1128,93 @@
   </si>
   <si>
     <t>журнал запросов PostgreSQL</t>
+  </si>
+  <si>
+    <t>После захода 30.09</t>
+  </si>
+  <si>
+    <t>После исполнения решений</t>
+  </si>
+  <si>
+    <t>Решения заказчика</t>
+  </si>
+  <si>
+    <t>8 ждут</t>
+  </si>
+  <si>
+    <t>исполнено 7: П-27, П-28, П-39, П-40, П-50, П-51, П-52; П-4 ждёт закрытого хранилища</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54: найдено П-54 — проверка графика, записанная под календарь, покраснела 01.10.2026 сама собой</t>
+  </si>
+  <si>
+    <t>Закрыто, всего</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>53: П-12 закрыт слиянием запроса #46; открыт П-4 — ждёт переноса</t>
+  </si>
+  <si>
+    <t>Дефект А-12 реестра 09_AUDIT.md</t>
+  </si>
+  <si>
+    <t>открыт</t>
+  </si>
+  <si>
+    <t>снят решением: публикация только с main</t>
+  </si>
+  <si>
+    <t>09_AUDIT.md, pages.yml</t>
+  </si>
+  <si>
+    <t>841</t>
+  </si>
+  <si>
+    <t>874: адреса экранов 18, предупреждение о закрытых траншах 6, гарнитуры из сборки 3</t>
+  </si>
+  <si>
+    <t>559</t>
+  </si>
+  <si>
+    <t>561</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>94: закрытые транши сметы, обезличивание заявки</t>
+  </si>
+  <si>
+    <t>Миграции</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20: дата снятия доступа, дата обезличивания заявки</t>
+  </si>
+  <si>
+    <t>apps/api/prisma/migrations</t>
+  </si>
+  <si>
+    <t>Зависимости</t>
+  </si>
+  <si>
+    <t>sharp 0.35.5 в apps/api — решением по П-39</t>
+  </si>
+  <si>
+    <t>apps/api/package.json</t>
+  </si>
+  <si>
+    <t>549,69 кБ JS, 74,6 кБ CSS</t>
+  </si>
+  <si>
+    <t>555,49 кБ JS (148,13 кБ gzip), 79,99 кБ CSS; гарнитуры — 18 файлов, 220 КБ</t>
   </si>
   <si>
     <t>Довод за правку</t>
@@ -1942,27 +2023,27 @@
         <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>13</v>
@@ -1970,22 +2051,22 @@
     </row>
     <row r="15" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>13</v>
@@ -1993,22 +2074,22 @@
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>13</v>
@@ -2016,22 +2097,22 @@
     </row>
     <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>13</v>
@@ -2039,22 +2120,22 @@
     </row>
     <row r="18" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>13</v>
@@ -2062,22 +2143,22 @@
     </row>
     <row r="19" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>13</v>
@@ -2085,22 +2166,22 @@
     </row>
     <row r="20" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>13</v>
@@ -2108,22 +2189,22 @@
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>13</v>
@@ -2131,22 +2212,22 @@
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>13</v>
@@ -2154,22 +2235,22 @@
     </row>
     <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>13</v>
@@ -2177,22 +2258,22 @@
     </row>
     <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>13</v>
@@ -2200,22 +2281,22 @@
     </row>
     <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>13</v>
@@ -2223,22 +2304,22 @@
     </row>
     <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>13</v>
@@ -2246,22 +2327,22 @@
     </row>
     <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>13</v>
@@ -2269,68 +2350,68 @@
     </row>
     <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>13</v>
@@ -2338,22 +2419,22 @@
     </row>
     <row r="31" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>13</v>
@@ -2361,22 +2442,22 @@
     </row>
     <row r="32" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>13</v>
@@ -2384,22 +2465,22 @@
     </row>
     <row r="33" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>13</v>
@@ -2407,22 +2488,22 @@
     </row>
     <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>13</v>
@@ -2430,22 +2511,22 @@
     </row>
     <row r="35" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>13</v>
@@ -2453,22 +2534,22 @@
     </row>
     <row r="36" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>13</v>
@@ -2476,22 +2557,22 @@
     </row>
     <row r="37" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>13</v>
@@ -2499,22 +2580,22 @@
     </row>
     <row r="38" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>13</v>
@@ -2522,22 +2603,22 @@
     </row>
     <row r="39" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>13</v>
@@ -2545,68 +2626,68 @@
     </row>
     <row r="40" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="G40" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="F41" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="G41" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="F42" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>13</v>
@@ -2614,22 +2695,22 @@
     </row>
     <row r="43" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="F43" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>13</v>
@@ -2637,22 +2718,22 @@
     </row>
     <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>13</v>
@@ -2660,22 +2741,22 @@
     </row>
     <row r="45" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>13</v>
@@ -2683,22 +2764,22 @@
     </row>
     <row r="46" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="F46" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>13</v>
@@ -2706,22 +2787,22 @@
     </row>
     <row r="47" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>13</v>
@@ -2729,22 +2810,22 @@
     </row>
     <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="F48" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>13</v>
@@ -2752,22 +2833,22 @@
     </row>
     <row r="49" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="F49" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>13</v>
@@ -2775,22 +2856,22 @@
     </row>
     <row r="50" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>13</v>
@@ -2798,91 +2879,91 @@
     </row>
     <row r="51" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="G51" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="F52" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="G52" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>272</v>
-      </c>
       <c r="G53" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>13</v>
@@ -2890,25 +2971,25 @@
     </row>
     <row r="55" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="F55" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="G55" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -2935,114 +3016,114 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3050,13 +3131,13 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3078,68 +3159,68 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -3151,7 +3232,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -3162,184 +3243,352 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>372</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -3361,101 +3610,101 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>377</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>380</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>383</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>386</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>389</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -110,10 +110,10 @@
     <t>git ls-files -s; решение Р-24</t>
   </si>
   <si>
-    <t>вынесено: раздел 3</t>
-  </si>
-  <si>
-    <t>решено 01.10.2026, в работе</t>
+    <t>решение 01.10.2026 (раздел 3) и уточнение 02.10.2026 (10_QUIZ.md): файл убран из публичного дерева 02.10.2026; перенос в закрытое priyomka-internal — после его создания: у интеграции GitHub нет права создавать хранилища, ответ 403. Прежние редакции остаются в истории — принято. Ссылки документов называют документ; README.md называет его место. Страж — verify-docs.mjs: файла в дереве нет; возврат файла даёт замечание</t>
+  </si>
+  <si>
+    <t>убрано из дерева 02.10.2026, перенос ждёт хранилища</t>
   </si>
   <si>
     <t>П-5</t>
@@ -1142,7 +1142,7 @@
     <t>8 ждут</t>
   </si>
   <si>
-    <t>исполнено 7: П-27, П-28, П-39, П-40, П-50, П-51, П-52; П-4 ждёт закрытого хранилища</t>
+    <t>исполнено 7: П-27, П-28, П-39, П-40, П-50, П-51, П-52; П-4 — файл убран из публичного дерева 02.10.2026, перенос ждёт закрытого хранилища</t>
   </si>
   <si>
     <t>53</t>
@@ -1157,7 +1157,7 @@
     <t>44</t>
   </si>
   <si>
-    <t>53: П-12 закрыт слиянием запроса #46; открыт П-4 — ждёт переноса</t>
+    <t>53: П-12 закрыт слиянием запроса #46; П-4 убран из дерева, перенос ждёт хранилища</t>
   </si>
   <si>
     <t>Дефект А-12 реестра 09_AUDIT.md</t>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -455,7 +455,7 @@
     <t>прогон на свежем стенде</t>
   </si>
   <si>
-    <t>решение 01.10.2026 (раздел 3): правило оставлено — акт следует за сметой, — правка предупреждает. Маршрут GET /projects/:code/estimate/closed-tranches (руководителю) отдаёт закрытые транши с принятыми в них позициями; листы правки позиции и надбавки при открытии называют задетые транши, подписанные акты с датой и оплаченные транши (closed-tranches.ts). Сторно приёмки в закрытом транше предупреждением не снабжено: решение называло листы правки позиции и надбавки. Стражи: closed-tranches.test.ts — 6 тестов; verify-api — только что закрытый транш называет принятую в нём позицию, прорабу и заказчику 403; verify-page — лист надбавки по настоящему перечню, лист позиции по подставленному ответу. Откат сервера (пустой перечень): verify-api — 1, verify-page — 1; компилирующийся откат клиента (лист не спрашивает перечень): verify-page — 4</t>
+    <t>решение 01.10.2026 (раздел 3): правило оставлено — акт следует за сметой, — правка предупреждает. Маршрут GET /projects/:code/estimate/closed-tranches (руководителю) отдаёт закрытые транши с принятыми в них позициями; листы правки позиции и надбавки при открытии называют задетые транши, подписанные акты с датой и оплаченные транши (closed-tranches.ts). Сторно добавлено заказчиком 02.10.2026: пакет приёмки называет свой транш (trancheNumber), лист сторно сверяет его с перечнем — пакет закрытого транша, подпись и оплата называются тем же текстом. Стражи: closed-tranches.test.ts — 6 тестов; verify-api — только что закрытый транш называет принятую в нём позицию, прорабу и заказчику 403; verify-page — лист надбавки по настоящему перечню, лист позиции по подставленному ответу. Откат сервера (пустой перечень): verify-api — 1, verify-page — 1; компилирующийся откат клиента (лист не спрашивает перечень): verify-page — 4; сторно: verify-api — пакет закрытого транша называет его номер, verify-page — лист сторно по настоящему номеру пакета и подставленному перечню; откат сервера (номер не отдаётся) — по 1 замечанию, откат клиента — 2</t>
   </si>
   <si>
     <t>закрыто 02.10.2026</t>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -650,7 +650,7 @@
     <t>чтение кода и плана</t>
   </si>
   <si>
-    <t>решение 01.10.2026 (раздел 3): действие «Обезличить» у отказной заявки — POST /leads/:id/anonymization, поле anonymizedAt (миграция 20261001010000_lead_anonymized_at); имя, телефон, адрес и заметка заменяются условным обновлением один раз, причина отказа, стадия, ориентир и задачи остаются; запись журнала о факте без персональных данных. Журнал заявки не трогается — решено заказчиком: запись «заявка заведена» хранит имя. Лист — через подтверждение с последствиями. verify-api: только отказная, однократно, прорабу 403, карточка без имени и телефона, журнал не переписан; verify-page: гейт и шапка листа после подтверждения. Откат замены полей: verify-api — 1 замечание, verify-page — 1. Срок хранения — вместе с политикой обработки (пункт 6.2 плана)</t>
+    <t>решение 01.10.2026 (раздел 3): действие «Обезличить» у отказной заявки — POST /leads/:id/anonymization, поле anonymizedAt (миграция 20261001010000_lead_anonymized_at); имя, телефон, адрес и заметка заменяются условным обновлением один раз, причина отказа, стадия, ориентир и задачи остаются; запись журнала о факте без персональных данных. Журнал заявки не трогается — решено заказчиком: запись «заявка заведена» хранит имя. Лист — через подтверждение с последствиями. verify-api: только отказная, однократно, прорабу 403, карточка без имени и телефона, журнал не переписан; verify-page: гейт и шапка листа после подтверждения. Откат замены полей: verify-api — 1 замечание, verify-page — 1. Срок хранения — вместе с политикой обработки (пункт 6.2 плана). Вариант «а» исполнен 02.10.2026 вместе с проектом политики (16_PD_POLICY.md): поле lostAt (миграция 20261002000000_lead_lost_at, дата прежних отказов — из журнала), LEAD_RETENTION_DAYS = 30 в домене (ч. 7 ст. 21 152-ФЗ), служба LeadRetentionService обезличивает отказные заявки при запуске сервера и раз в шесть часов, запись журнала без автора и без персональных данных. Стражи: тесты домена — граница 30 дней; verify-api — отказная заявка наполнения с отказом 45 дней назад обезличена, с отказом 10 дней назад — нет. Откат обхода — 2 замечания</t>
   </si>
   <si>
     <t>П-41</t>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="430">
   <si>
     <t>№</t>
   </si>
@@ -863,6 +863,21 @@
     <t>месяц сегодняшнего дня выводится из часов: в сентябре отметка ожидается только если сегодня сентябрь, затем обход шагает к месяцу сегодняшнего дня (не дальше двух лет) и ищет отметку там. Прежнее правило 01.10.2026 падает, новое проходит; за двумя годами — именованное «наполнение устарело» вместо молчаливого пропуска</t>
   </si>
   <si>
+    <t>П-55</t>
+  </si>
+  <si>
+    <t>docker-compose.yml:19 (служба minio)</t>
+  </si>
+  <si>
+    <t>docker compose up из чистого клона не поднимался: образа minio/minio:RELEASE.2024-12-18T13-15-44Z в Docker Hub нет, загрузка падала «not found». Пункт плана 0.17 стоял «написан, не запускался» с 03.09.2026, а хранилище S3 кодом не читалось вовсе — файлы лежат на томе</t>
+  </si>
+  <si>
+    <t>первый запуск поставки 02.10.2026: демон Docker поднят в среде, образы собраны, docker compose up упал на загрузке MinIO</t>
+  </si>
+  <si>
+    <t>служба MinIO и её том сняты, ключи S3 в .env.example оставлены пометкой для адаптера облака (план 6.1). Поставка по .env.example поднимает базу, сервер с применёнными миграциями и клиент; сервер отвечает через nginx клиента, код входа в ответ не попадает, sharp грузится в образе Alpine. Страж — работа CI «Поставка» (ci.yml). Откат: прежний docker-compose.yml падает на загрузке образа MinIO, новый поднимается</t>
+  </si>
+  <si>
     <t>Вопрос</t>
   </si>
   <si>
@@ -989,10 +1004,7 @@
     <t>docker compose up из чистого клона</t>
   </si>
   <si>
-    <t>демона Docker в среде нет (пункт 0.17 плана)</t>
-  </si>
-  <si>
-    <t>запуск на машине с Docker</t>
+    <t>снято 02.10.2026: демон Docker поднят в среде, поставка проверена и держится работой CI «Поставка» (П-55)</t>
   </si>
   <si>
     <t>Величина</t>
@@ -1715,7 +1727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2990,6 +3002,29 @@
       </c>
       <c r="G55" s="2" t="s">
         <v>153</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3016,16 +3051,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3033,13 +3068,13 @@
         <v>142</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3047,13 +3082,13 @@
         <v>262</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3061,13 +3096,13 @@
         <v>148</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3075,13 +3110,13 @@
         <v>257</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3089,13 +3124,13 @@
         <v>207</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3103,13 +3138,13 @@
         <v>202</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3117,13 +3152,13 @@
         <v>267</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3131,13 +3166,13 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3159,68 +3194,68 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -3243,352 +3278,352 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3610,101 +3645,101 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="445">
   <si>
     <t>№</t>
   </si>
@@ -101,7 +101,7 @@
     <t>решение заказчика</t>
   </si>
   <si>
-    <t>docs/04_REFERENCE_STWORKA.md</t>
+    <t>разбор эталона</t>
   </si>
   <si>
     <t>Разбор эталона помечен «права 600, наружу не выносится», но git права 600 не хранит (в индексе 100644), а репозиторий публичен с 09.09.2026 вместе с историей</t>
@@ -953,7 +953,7 @@
     <t>а</t>
   </si>
   <si>
-    <t>04_REFERENCE_STWORKA.md помечен «наружу не выносится», а хранилище публично вместе с историей</t>
+    <t>Разбор эталона помечен «наружу не выносится», а хранилище публично вместе с историей</t>
   </si>
   <si>
     <t>а) убрать файл из рабочего дерева в закрытое хранилище; история сохранит прежние редакции — это надо принять; б) переписать историю — запрещено правилами захода и ломает все клоны; в) снять пометку, признав разбор публичным</t>
@@ -1148,6 +1148,9 @@
     <t>После исполнения решений</t>
   </si>
   <si>
+    <t>После доделки 02.10.2026</t>
+  </si>
+  <si>
     <t>Решения заказчика</t>
   </si>
   <si>
@@ -1157,10 +1160,16 @@
     <t>исполнено 7: П-27, П-28, П-39, П-40, П-50, П-51, П-52; П-4 — файл убран из публичного дерева 02.10.2026, перенос ждёт закрытого хранилища</t>
   </si>
   <si>
+    <t>без изменений; П-40 дополнен обезличиванием по сроку хранения</t>
+  </si>
+  <si>
     <t>53</t>
   </si>
   <si>
-    <t>54: найдено П-54 — проверка графика, записанная под календарь, покраснела 01.10.2026 сама собой</t>
+    <t>55: П-54 — проверка графика, записанная под календарь, покраснела 01.10.2026 сама собой; П-55 — поставка Docker не поднималась из чистого клона</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t>Закрыто, всего</t>
@@ -1169,39 +1178,66 @@
     <t>44</t>
   </si>
   <si>
-    <t>53: П-12 закрыт слиянием запроса #46; П-4 убран из дерева, перенос ждёт хранилища</t>
-  </si>
-  <si>
-    <t>Дефект А-12 реестра 09_AUDIT.md</t>
-  </si>
-  <si>
-    <t>открыт</t>
-  </si>
-  <si>
-    <t>снят решением: публикация только с main</t>
+    <t>54: П-12 закрыт слиянием запроса #46; П-4 убран из дерева, перенос ждёт хранилища</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Дефекты реестра 09_AUDIT.md</t>
+  </si>
+  <si>
+    <t>А-11, А-12 открыты</t>
+  </si>
+  <si>
+    <t>А-12 снят решением: публикация только с main</t>
+  </si>
+  <si>
+    <t>А-11 закрыт: модульные тесты сервера</t>
   </si>
   <si>
     <t>09_AUDIT.md, pages.yml</t>
   </si>
   <si>
+    <t>Пункты плана</t>
+  </si>
+  <si>
+    <t>4.10 (скан подписанного акта), 6.4 (памятка прорабу) ✔; 6.2 ◐ — проект политики ждёт юриста</t>
+  </si>
+  <si>
+    <t>06_PLAN.md</t>
+  </si>
+  <si>
     <t>841</t>
   </si>
   <si>
     <t>874: адреса экранов 18, предупреждение о закрытых траншах 6, гарнитуры из сборки 3</t>
   </si>
   <si>
+    <t>913, из них сервер 28</t>
+  </si>
+  <si>
     <t>559</t>
   </si>
   <si>
+    <t>573</t>
+  </si>
+  <si>
     <t>561</t>
   </si>
   <si>
+    <t>566</t>
+  </si>
+  <si>
     <t>92</t>
   </si>
   <si>
     <t>94: закрытые транши сметы, обезличивание заявки</t>
   </si>
   <si>
+    <t>96: приложить и открыть скан акта</t>
+  </si>
+  <si>
     <t>Миграции</t>
   </si>
   <si>
@@ -1211,6 +1247,9 @@
     <t>20: дата снятия доступа, дата обезличивания заявки</t>
   </si>
   <si>
+    <t>22: дата отказа заявки, скан акта</t>
+  </si>
+  <si>
     <t>apps/api/prisma/migrations</t>
   </si>
   <si>
@@ -1220,6 +1259,9 @@
     <t>sharp 0.35.5 в apps/api — решением по П-39</t>
   </si>
   <si>
+    <t>без изменений</t>
+  </si>
+  <si>
     <t>apps/api/package.json</t>
   </si>
   <si>
@@ -1227,6 +1269,9 @@
   </si>
   <si>
     <t>555,49 кБ JS (148,13 кБ gzip), 79,99 кБ CSS; гарнитуры — 18 файлов, 220 КБ</t>
+  </si>
+  <si>
+    <t>557,25 кБ JS (148,66 кБ gzip), 80,01 кБ CSS</t>
   </si>
   <si>
     <t>Довод за правку</t>
@@ -3267,13 +3312,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3458,7 +3504,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>330</v>
       </c>
@@ -3469,165 +3515,218 @@
         <v>376</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>334</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="17" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="C21" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="C22" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="22" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="B23" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="C25" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="B26" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>371</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:E1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3648,98 +3747,98 @@
         <v>315</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>415</v>
+        <v>430</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="454">
   <si>
     <t>№</t>
   </si>
@@ -878,6 +878,24 @@
     <t>служба MinIO и её том сняты, ключи S3 в .env.example оставлены пометкой для адаптера облака (план 6.1). Поставка по .env.example поднимает базу, сервер с применёнными миграциями и клиент; сервер отвечает через nginx клиента, код входа в ответ не попадает, sharp грузится в образе Alpine. Страж — работа CI «Поставка» (ci.yml). Откат: прежний docker-compose.yml падает на загрузке образа MinIO, новый поднимается</t>
   </si>
   <si>
+    <t>П-56</t>
+  </si>
+  <si>
+    <t>apps/api/src/projects/projects.service.ts:617 (toSummary), apps/web/src/ProjectCard.tsx:511</t>
+  </si>
+  <si>
+    <t>Сводка объекта не знала роли: GET /projects и GET /projects/:code отдавали заказчику ориентир по заявке (вилка, ставка за м², отклонение сметы от вилки), потраченное на материалы, остаток текущего транша и «выполнено на сумму», прорабу — ориентир, то есть сведения закрытого ему раздела «Заявки». Карточка выводила эти величины без проверки роли. Класс П-1, П-16, П-17</t>
+  </si>
+  <si>
+    <t>сверка продукта со вторым референсом 05.10.2026, чтение кода; прогон: ключ guideline в каждом объекте у прораба и заказчика, у заказчика — spentMaterials, trancheRemainder, accepted</t>
+  </si>
+  <si>
+    <t>этап Э8, ДР-0: toSummary получает роль; поле вне проекции отсутствует в ответе, а не равно null; ориентир не выбирается из базы для ролей, которым не положен; контракт — необязательные поля; карточка следует за ответом. Стенд получил объект из заявки (R-99, вымышленная заявка № 1001), иначе утечку ориентира было не на чем увидеть. Попутно: предел высоты липкой сводки учитывает поле конца страницы — сводка с ориентиром уходила верхом за экран на 46 px. Стражи: verify-api — четыре роли, список и карточка каждого видимого объекта, ключи обеих половин; verify-page и verify-demo — подписи сводки R-99 по ролям. Откат сериализатора к сводке без роли (компилируется): verify-api — 20 замечаний «ДР-0», verify-page — 4; слепок прежнего сервера в демонстрации — 3</t>
+  </si>
+  <si>
+    <t>закрыто 05.10.2026</t>
+  </si>
+  <si>
     <t>Вопрос</t>
   </si>
   <si>
@@ -1272,6 +1290,15 @@
   </si>
   <si>
     <t>557,25 кБ JS (148,66 кБ gzip), 80,01 кБ CSS</t>
+  </si>
+  <si>
+    <t>Этап Э8</t>
+  </si>
+  <si>
+    <t>56: П-56 — сводка объекта без проекции роли</t>
+  </si>
+  <si>
+    <t>этот реестр</t>
   </si>
   <si>
     <t>Довод за правку</t>
@@ -1772,7 +1799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3070,6 +3097,29 @@
       </c>
       <c r="G56" s="2" t="s">
         <v>147</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -3096,16 +3146,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3113,13 +3163,13 @@
         <v>142</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3127,13 +3177,13 @@
         <v>262</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3141,13 +3191,13 @@
         <v>148</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3155,13 +3205,13 @@
         <v>257</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3169,13 +3219,13 @@
         <v>207</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3183,13 +3233,13 @@
         <v>202</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3197,13 +3247,13 @@
         <v>267</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3211,13 +3261,13 @@
         <v>26</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -3239,68 +3289,68 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -3312,7 +3362,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -3324,405 +3374,447 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -3744,101 +3836,101 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -1313,7 +1313,7 @@
     <t>сторно платежа — денежное событие, его ищут в журнале</t>
   </si>
   <si>
-    <t>записанное решение «приёмки в ленте нет намеренно» распространяется по той же логике: вкладка «Транши» показывает платежи со сторно подробнее ленты; изменение — отмена записанного решения</t>
+    <t>записанное решение «приёмки в ленте нет намеренно» распространяется по той же логике: вкладка «Транши» показывает платежи со сторно подробнее ленты; изменение — отмена записанного решения *Правка 05.10.2026: решение «приёмки в ленте нет намеренно» отменено этапом Э8 (ДР-5, допущение В7) — пакет приёмки, сторно, платёж и его сторно, решение по чеку, закрытие транша и подпись акта идут в ленту по проекции роли; шум снимает отбор по видам*</t>
   </si>
   <si>
     <t>Экран кода показывает номер целиком</t>

--- a/docs/13_FULL_AUDIT.xlsx
+++ b/docs/13_FULL_AUDIT.xlsx
@@ -455,7 +455,7 @@
     <t>прогон на свежем стенде</t>
   </si>
   <si>
-    <t>решение 01.10.2026 (раздел 3): правило оставлено — акт следует за сметой, — правка предупреждает. Маршрут GET /projects/:code/estimate/closed-tranches (руководителю) отдаёт закрытые транши с принятыми в них позициями; листы правки позиции и надбавки при открытии называют задетые транши, подписанные акты с датой и оплаченные транши (closed-tranches.ts). Сторно добавлено заказчиком 02.10.2026: пакет приёмки называет свой транш (trancheNumber), лист сторно сверяет его с перечнем — пакет закрытого транша, подпись и оплата называются тем же текстом. Стражи: closed-tranches.test.ts — 6 тестов; verify-api — только что закрытый транш называет принятую в нём позицию, прорабу и заказчику 403; verify-page — лист надбавки по настоящему перечню, лист позиции по подставленному ответу. Откат сервера (пустой перечень): verify-api — 1, verify-page — 1; компилирующийся откат клиента (лист не спрашивает перечень): verify-page — 4; сторно: verify-api — пакет закрытого транша называет его номер, verify-page — лист сторно по настоящему номеру пакета и подставленному перечню; откат сервера (номер не отдаётся) — по 1 замечанию, откат клиента — 2</t>
+    <t>решение 01.10.2026 (раздел 3): правило оставлено — акт следует за сметой, — правка предупреждает. Маршрут GET /projects/:code/estimate/closed-tranches (руководителю) отдаёт закрытые транши с принятыми в них позициями; листы правки позиции и надбавки при открытии называют задетые транши, подписанные акты с датой и оплаченные транши (closed-tranches.ts). Сторно добавлено заказчиком 02.10.2026: пакет приёмки называет свой транш (trancheNumber), лист сторно сверяет его с перечнем — пакет закрытого транша, подпись и оплата называются тем же текстом. Стражи: closed-tranches.test.ts — 6 тестов; verify-api — только что закрытый транш называет принятую в нём позицию, прорабу и заказчику 403; verify-page — лист надбавки по настоящему перечню, лист позиции по подставленному ответу. Откат сервера (пустой перечень): verify-api — 1, verify-page — 1; компилирующийся откат клиента (лист не спрашивает перечень): verify-page — 4; сторно: verify-api — пакет закрытого транша называет его номер, verify-page — лист сторно по настоящему номеру пакета и подставленному перечню; откат сервера (номер не отдаётся) — по 1 замечанию, откат клиента — 2 С 07.10.2026 (этап Э9, ДР-3) подписанный акт зафиксирован: строки и надбавка — снимок при первой отметке подписания, правка сметы его не меняет, сторно его пакета запрещено, ошибка исправляется поправкой строкой акта текущего транша; предупреждение листов называет такой акт зафиксированным</t>
   </si>
   <si>
     <t>закрыто 02.10.2026</t>
